--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.061551228686622</v>
+        <v>1.19545168271532</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.06155122868662644</v>
+        <v>0.195451682715311</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.01138178742316343</v>
+        <v>0.03440420876732841</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.02869674544650302</v>
+        <v>0.0521133129619058</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2623858934112292</v>
+        <v>0.2004827069678456</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1177613797581724</v>
+        <v>0.1944460881392946</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1674465387521203</v>
+        <v>0.2826241740756946</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.4124988609057635</v>
+        <v>0.3752012490863208</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.02759228812940559</v>
+        <v>0.09169534710001245</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2164079610303172</v>
+        <v>0.1562850236871939</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2054030134905857</v>
+        <v>0.3361486556537671</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3457651525215044</v>
+        <v>0.1998343001131861</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2024年02月-2025年06月</t>
+          <t>2024年02月-2025年12月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>25.83954877233163</v>
+        <v>19.2420631566089</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.1030804204825524</v>
+        <v>0.07676140085150943</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2394987042350557</v>
+        <v>0.1844445226341943</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2.601503759398496</v>
+        <v>8.624812030075187</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.19545168271532</v>
+        <v>0.799815593937401</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.195451682715311</v>
+        <v>-0.2001844060625947</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.03440420876732841</v>
+        <v>-0.04144037410997015</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.0521133129619058</v>
+        <v>-0.02502973681004239</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2004827069678456</v>
+        <v>0.2117581535473875</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1944460881392946</v>
+        <v>-0.1641986751489507</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2826241740756946</v>
+        <v>-0.2292466223530472</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.3752012490863208</v>
+        <v>0.4841208315786298</v>
       </c>
     </row>
     <row r="14">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.09169534710001245</v>
+        <v>-0.08559923764247168</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.1562850236871939</v>
+        <v>0.1850802356664543</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3361486556537671</v>
+        <v>-0.1146447954654385</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.1998343001131861</v>
+        <v>0.3643033381451197</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2024年02月-2025年12月</t>
+          <t>2021年09月-2025年10月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>19.2420631566089</v>
+        <v>19.10702643452143</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.07676140085150943</v>
+        <v>0.07622270560508673</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.1844445226341943</v>
+        <v>0.1834734211998591</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>8.624812030075187</v>
+        <v>3.218045112781955</v>
       </c>
     </row>
     <row r="24">
